--- a/TitanSiege/Data/Excel/技能配置表.xlsx
+++ b/TitanSiege/Data/Excel/技能配置表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30048" windowHeight="13620" activeTab="2"/>
+    <workbookView windowWidth="30048" windowHeight="13620" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="效果list" sheetId="1" r:id="rId1"/>
@@ -1271,7 +1271,7 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G2" t="s">
         <v>23</v>
@@ -1306,7 +1306,7 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="G3">
         <v>3</v>
@@ -1341,7 +1341,7 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>300</v>
+        <v>70</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -1376,7 +1376,7 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>220</v>
+        <v>70</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -1411,7 +1411,7 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G6">
         <v>0</v>

--- a/TitanSiege/Data/Excel/技能配置表.xlsx
+++ b/TitanSiege/Data/Excel/技能配置表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30048" windowHeight="13620" activeTab="1"/>
+    <workbookView windowWidth="30048" windowHeight="13620" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="效果list" sheetId="1" r:id="rId1"/>
@@ -1268,7 +1268,7 @@
         <v>22</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>50</v>
@@ -1303,7 +1303,7 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>60</v>
@@ -1338,7 +1338,7 @@
         <v>31</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <v>70</v>
@@ -1373,7 +1373,7 @@
         <v>35</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
         <v>70</v>
@@ -1408,7 +1408,7 @@
         <v>39</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1477,7 +1477,7 @@
         <v>0.2</v>
       </c>
       <c r="D2">
-        <v>120</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>30</v>
@@ -1497,7 +1497,7 @@
         <v>0.4</v>
       </c>
       <c r="D3">
-        <v>120</v>
+        <v>3</v>
       </c>
       <c r="E3">
         <v>30</v>
@@ -1517,7 +1517,7 @@
         <v>0.8</v>
       </c>
       <c r="D4">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="E4">
         <v>360</v>
@@ -1537,7 +1537,7 @@
         <v>0.4</v>
       </c>
       <c r="D5">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="E5">
         <v>360</v>
@@ -1557,7 +1557,7 @@
         <v>0.4</v>
       </c>
       <c r="D6">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="E6">
         <v>360</v>
@@ -1577,7 +1577,7 @@
         <v>0.4</v>
       </c>
       <c r="D7">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="E7">
         <v>360</v>
@@ -1597,7 +1597,7 @@
         <v>0.2</v>
       </c>
       <c r="D8">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="E8">
         <v>30</v>

--- a/TitanSiege/Data/Excel/技能配置表.xlsx
+++ b/TitanSiege/Data/Excel/技能配置表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30048" windowHeight="13620" activeTab="2"/>
+    <workbookView windowWidth="23040" windowHeight="9300" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="效果list" sheetId="1" r:id="rId1"/>
@@ -1477,10 +1477,10 @@
         <v>0.2</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
@@ -1497,10 +1497,10 @@
         <v>0.4</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
@@ -1517,7 +1517,7 @@
         <v>0.8</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E4">
         <v>360</v>
@@ -1600,7 +1600,7 @@
         <v>2</v>
       </c>
       <c r="E8">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
